--- a/reports/travelsync_unified_report.xlsx
+++ b/reports/travelsync_unified_report.xlsx
@@ -51,37 +51,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t>Test Domain</t>
-        </is>
+      <c r="A1" t="str" s="1">
+        <v>Test Domain</v>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t>Total Cases</t>
-        </is>
+      <c r="B1" t="str" s="1">
+        <v>Total Cases</v>
       </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t>Passed</t>
-        </is>
+      <c r="C1" t="str" s="1">
+        <v>Passed</v>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>Failed</t>
-        </is>
+      <c r="D1" t="str" s="1">
+        <v>Failed</v>
       </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t>Status</t>
-        </is>
+      <c r="E1" t="str" s="1">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Functional Testing</t>
-        </is>
+      <c r="A2" t="str">
+        <v>Functional Testing</v>
       </c>
       <c r="B2" t="n">
         <v>300</v>
@@ -92,17 +80,13 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E2" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Load &amp; Stress Testing</t>
-        </is>
+      <c r="A3" t="str">
+        <v>Load &amp; Stress Testing</v>
       </c>
       <c r="B3" t="n">
         <v>300</v>
@@ -113,17 +97,13 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E3" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Security &amp; Vulnerability Audit</t>
-        </is>
+      <c r="A4" t="str">
+        <v>Security &amp; Vulnerability Audit</v>
       </c>
       <c r="B4" t="n">
         <v>300</v>
@@ -134,17 +114,13 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E4" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Web Unit Tests</t>
-        </is>
+      <c r="A5" t="str">
+        <v>Web Unit Tests</v>
       </c>
       <c r="B5" t="n">
         <v>50</v>
@@ -155,17 +131,13 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E5" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Web E2E Browser Tests</t>
-        </is>
+      <c r="A6" t="str">
+        <v>Web E2E Browser Tests</v>
       </c>
       <c r="B6" t="n">
         <v>50</v>
@@ -176,17 +148,13 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E6" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mobile Appium E2E Tests</t>
-        </is>
+      <c r="A7" t="str">
+        <v>Mobile Appium E2E Tests</v>
       </c>
       <c r="B7" t="n">
         <v>50</v>
@@ -197,17 +165,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
+      <c r="E7" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Total Pipeline Summary</t>
-        </is>
+      <c r="A8" t="str">
+        <v>Total Pipeline Summary</v>
       </c>
       <c r="B8" t="n">
         <v>1050</v>
@@ -218,10 +182,8 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>100% PASSED</t>
-        </is>
+      <c r="E8" t="str">
+        <v>100% PASSED</v>
       </c>
     </row>
   </sheetData>
